--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/车辆信息导入模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/车辆信息导入模版.xlsx
@@ -1398,7 +1398,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
